--- a/golf_streamlit/data/rundeinfo.xlsx
+++ b/golf_streamlit/data/rundeinfo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,18 +462,18 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202502</v>
+        <v>202601</v>
       </c>
       <c r="B2" t="n">
-        <v>20250203</v>
+        <v>20260101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Payne’s Valley</t>
+          <t>Meland</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -487,21 +487,21 @@
         <v>202502</v>
       </c>
       <c r="B3" t="n">
-        <v>20250202</v>
+        <v>20250203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St Andrews – Castle</t>
+          <t>The Club at Olde Stone</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -509,15 +509,15 @@
         <v>202502</v>
       </c>
       <c r="B4" t="n">
-        <v>20250201</v>
+        <v>20250202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miklagard</t>
+          <t>St Andrews – Castle</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -528,18 +528,18 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202501</v>
+        <v>202502</v>
       </c>
       <c r="B5" t="n">
-        <v>20250105</v>
+        <v>20250201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Haugaland</t>
+          <t>Miklagard</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -553,15 +553,15 @@
         <v>202501</v>
       </c>
       <c r="B6" t="n">
-        <v>20250104</v>
+        <v>20250105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meland</t>
+          <t>Haugaland</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -575,15 +575,15 @@
         <v>202501</v>
       </c>
       <c r="B7" t="n">
-        <v>20250103</v>
+        <v>20250104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bjørnefjorden</t>
+          <t>Meland</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -597,15 +597,15 @@
         <v>202501</v>
       </c>
       <c r="B8" t="n">
-        <v>20250102</v>
+        <v>20250103</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Herdla</t>
+          <t>Bjørnefjorden</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -619,15 +619,15 @@
         <v>202501</v>
       </c>
       <c r="B9" t="n">
-        <v>20250101</v>
+        <v>20250102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fana</t>
+          <t>Herdla</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -638,18 +638,18 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202402</v>
+        <v>202501</v>
       </c>
       <c r="B10" t="n">
-        <v>20240203</v>
+        <v>20250101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Franklin Hills CC</t>
+          <t>Fana</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -663,15 +663,15 @@
         <v>202402</v>
       </c>
       <c r="B11" t="n">
-        <v>20240202</v>
+        <v>20240203</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St Andrews – Old</t>
+          <t>Franklin Hills CC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -685,15 +685,15 @@
         <v>202402</v>
       </c>
       <c r="B12" t="n">
-        <v>20240201</v>
+        <v>20240202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Crans-sur-Sierre (Ballesteros)</t>
+          <t>St Andrews – Old</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -704,18 +704,18 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202401</v>
+        <v>202402</v>
       </c>
       <c r="B13" t="n">
-        <v>20240106</v>
+        <v>20240201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meland</t>
+          <t>Crans-sur-Sierre (Ballesteros)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>106</v>
+        <v>201</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -729,15 +729,15 @@
         <v>202401</v>
       </c>
       <c r="B14" t="n">
-        <v>20240105</v>
+        <v>20240106</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sotra</t>
+          <t>Meland</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -751,15 +751,15 @@
         <v>202401</v>
       </c>
       <c r="B15" t="n">
-        <v>20240104</v>
+        <v>20240105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Sotra</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -773,15 +773,15 @@
         <v>202401</v>
       </c>
       <c r="B16" t="n">
-        <v>20240103</v>
+        <v>20240104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Voss</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -795,15 +795,15 @@
         <v>202401</v>
       </c>
       <c r="B17" t="n">
-        <v>20240102</v>
+        <v>20240103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fana</t>
+          <t>Voss</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -817,20 +817,42 @@
         <v>202401</v>
       </c>
       <c r="B18" t="n">
+        <v>20240102</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fana</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>102</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>202401</v>
+      </c>
+      <c r="B19" t="n">
         <v>20240101</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Bjørnefjorden</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>101</v>
       </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
         <v>1</v>
       </c>
     </row>
